--- a/Economically Disadvantage Youth 2024 - 2025.xlsx
+++ b/Economically Disadvantage Youth 2024 - 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4e48f910b33dede5/Documents/GIS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="8_{01E6BC6C-ADD4-478F-BE30-8020999151DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD776761-ECEB-4FA9-A2CD-F4293EE1395B}"/>
+  <xr:revisionPtr revIDLastSave="96" documentId="8_{01E6BC6C-ADD4-478F-BE30-8020999151DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BFB2C0D2-B358-4A4E-B62F-D2644A70D9FA}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{3B60B1A6-21E6-47B5-B77B-01E58CEBB0FE}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{3B60B1A6-21E6-47B5-B77B-01E58CEBB0FE}"/>
   </bookViews>
   <sheets>
     <sheet name="EnrollmentTrendsByStudentGroup" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="239">
   <si>
     <t>&lt;0.1%</t>
   </si>
@@ -246,9 +246,6 @@
     <t>91.1%</t>
   </si>
   <si>
-    <t>91.2%</t>
-  </si>
-  <si>
     <t>7.1%</t>
   </si>
   <si>
@@ -360,9 +357,6 @@
     <t>2.9%</t>
   </si>
   <si>
-    <t>88.5%</t>
-  </si>
-  <si>
     <t>90.1%</t>
   </si>
   <si>
@@ -396,9 +390,6 @@
     <t>17.7%</t>
   </si>
   <si>
-    <t>94.4%</t>
-  </si>
-  <si>
     <t>23.4%</t>
   </si>
   <si>
@@ -414,18 +405,9 @@
     <t>19.1%</t>
   </si>
   <si>
-    <t>95.0%</t>
-  </si>
-  <si>
-    <t>33.5%</t>
-  </si>
-  <si>
     <t>17.5%</t>
   </si>
   <si>
-    <t>24.5%</t>
-  </si>
-  <si>
     <t>19.5%</t>
   </si>
   <si>
@@ -450,24 +432,12 @@
     <t>35.0%</t>
   </si>
   <si>
-    <t>25.2%</t>
-  </si>
-  <si>
-    <t>34.1%</t>
-  </si>
-  <si>
-    <t>23.2%</t>
-  </si>
-  <si>
     <t>80.6%</t>
   </si>
   <si>
     <t>30.7%</t>
   </si>
   <si>
-    <t>28.6%</t>
-  </si>
-  <si>
     <t>42.5%</t>
   </si>
   <si>
@@ -477,27 +447,15 @@
     <t>41.6%</t>
   </si>
   <si>
-    <t>53.3%</t>
-  </si>
-  <si>
     <t>58.3%</t>
   </si>
   <si>
-    <t>56.1%</t>
-  </si>
-  <si>
     <t>31.0%</t>
   </si>
   <si>
     <t>58.6%</t>
   </si>
   <si>
-    <t>57.8%</t>
-  </si>
-  <si>
-    <t>73.4%</t>
-  </si>
-  <si>
     <t>Woodlynne School District</t>
   </si>
   <si>
@@ -573,9 +531,6 @@
     <t>3770</t>
   </si>
   <si>
-    <t>Mt. Ephraim School District</t>
-  </si>
-  <si>
     <t>3420</t>
   </si>
   <si>
@@ -648,9 +603,6 @@
     <t>1799</t>
   </si>
   <si>
-    <t>47.5%</t>
-  </si>
-  <si>
     <t>Gloucester Township Public Schools</t>
   </si>
   <si>
@@ -699,18 +651,12 @@
     <t>0680</t>
   </si>
   <si>
-    <t>70.7%</t>
-  </si>
-  <si>
     <t>Brooklawn Public School District</t>
   </si>
   <si>
     <t>0580</t>
   </si>
   <si>
-    <t>44.9%</t>
-  </si>
-  <si>
     <t>Black Horse Pike Regional School District</t>
   </si>
   <si>
@@ -802,6 +748,9 @@
   </si>
   <si>
     <t>This worksheet contains one table spanning columns A through O, with row 4 as the header row.</t>
+  </si>
+  <si>
+    <t>Mount Ephraim School District</t>
   </si>
 </sst>
 </file>
@@ -861,7 +810,10 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -898,8 +850,8 @@
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Table Style 1" pivot="0" count="2" xr9:uid="{51EBFCC2-16D4-438B-BBA4-93A944CEDCAC}">
-      <tableStyleElement type="wholeTable" dxfId="1"/>
-      <tableStyleElement type="headerRow" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="2"/>
+      <tableStyleElement type="headerRow" dxfId="1"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -911,6 +863,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -928,7 +884,7 @@
     <tableColumn id="6" xr3:uid="{23DB2919-0D1C-4E28-A0B4-E031ECD38330}" name="Female"/>
     <tableColumn id="7" xr3:uid="{5F360E3A-EF56-47DB-B68D-7A379F021F73}" name="Male"/>
     <tableColumn id="8" xr3:uid="{E452C04C-38F0-4B6C-89B2-44C9BD7DE502}" name="Non-Binary/Undesignated Gender"/>
-    <tableColumn id="9" xr3:uid="{F3B4F707-0AB1-4FAE-A97B-4604060BB6FC}" name="Economically Disadvantaged Students"/>
+    <tableColumn id="9" xr3:uid="{F3B4F707-0AB1-4FAE-A97B-4604060BB6FC}" name="Economically Disadvantaged Students" dataDxfId="0"/>
     <tableColumn id="10" xr3:uid="{850A556E-B5EE-4042-95DB-8E7196BF7ECE}" name="Students with Disabilities"/>
     <tableColumn id="11" xr3:uid="{0C14FFD3-BC37-46DC-96B5-7965F2147B73}" name="Multilingual Learners"/>
     <tableColumn id="12" xr3:uid="{0ADFFA91-21CA-4BBD-A260-CB2489BB3C59}" name="Students Experiencing Homelessness"/>
@@ -1248,81 +1204,81 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>255</v>
+        <v>237</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="B3" t="s">
-        <v>252</v>
+        <v>234</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>251</v>
+        <v>233</v>
       </c>
       <c r="B4" t="s">
-        <v>250</v>
+        <v>232</v>
       </c>
       <c r="C4" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="D4" t="s">
-        <v>248</v>
+        <v>230</v>
       </c>
       <c r="E4" t="s">
-        <v>247</v>
+        <v>229</v>
       </c>
       <c r="F4" t="s">
-        <v>246</v>
+        <v>228</v>
       </c>
       <c r="G4" t="s">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="H4" t="s">
-        <v>244</v>
+        <v>226</v>
       </c>
       <c r="I4" t="s">
-        <v>243</v>
+        <v>225</v>
       </c>
       <c r="J4" t="s">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="K4" t="s">
-        <v>241</v>
+        <v>223</v>
       </c>
       <c r="L4" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="M4" t="s">
-        <v>239</v>
+        <v>221</v>
       </c>
       <c r="N4" t="s">
-        <v>238</v>
+        <v>220</v>
       </c>
       <c r="O4" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="B5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C5" t="s">
-        <v>236</v>
+        <v>218</v>
       </c>
       <c r="D5" t="s">
-        <v>235</v>
+        <v>217</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1336,11 +1292,11 @@
       <c r="H5" t="s">
         <v>5</v>
       </c>
-      <c r="I5" t="s">
-        <v>129</v>
+      <c r="I5">
+        <v>25</v>
       </c>
       <c r="J5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K5" t="s">
         <v>62</v>
@@ -1360,16 +1316,16 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="B6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C6" t="s">
-        <v>234</v>
+        <v>216</v>
       </c>
       <c r="D6" t="s">
-        <v>233</v>
+        <v>215</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1383,8 +1339,8 @@
       <c r="H6" t="s">
         <v>5</v>
       </c>
-      <c r="I6" t="s">
-        <v>139</v>
+      <c r="I6">
+        <v>34</v>
       </c>
       <c r="J6" t="s">
         <v>33</v>
@@ -1407,16 +1363,16 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="B7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C7" t="s">
-        <v>232</v>
+        <v>214</v>
       </c>
       <c r="D7" t="s">
-        <v>231</v>
+        <v>213</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1430,14 +1386,14 @@
       <c r="H7" t="s">
         <v>5</v>
       </c>
-      <c r="I7" t="s">
-        <v>152</v>
+      <c r="I7">
+        <v>58</v>
       </c>
       <c r="J7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="K7" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="L7" t="s">
         <v>41</v>
@@ -1454,16 +1410,16 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="B8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C8" t="s">
-        <v>230</v>
+        <v>212</v>
       </c>
       <c r="D8" t="s">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1477,8 +1433,8 @@
       <c r="H8" t="s">
         <v>5</v>
       </c>
-      <c r="I8" t="s">
-        <v>138</v>
+      <c r="I8">
+        <v>25</v>
       </c>
       <c r="J8" t="s">
         <v>54</v>
@@ -1501,16 +1457,16 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="B9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C9" t="s">
-        <v>228</v>
+        <v>210</v>
       </c>
       <c r="D9" t="s">
-        <v>227</v>
+        <v>209</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1524,14 +1480,14 @@
       <c r="H9" t="s">
         <v>5</v>
       </c>
-      <c r="I9" t="s">
-        <v>147</v>
+      <c r="I9">
+        <v>53</v>
       </c>
       <c r="J9" t="s">
         <v>55</v>
       </c>
       <c r="K9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L9" t="s">
         <v>16</v>
@@ -1548,16 +1504,16 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="B10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C10" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="D10" t="s">
-        <v>225</v>
+        <v>207</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1571,11 +1527,11 @@
       <c r="H10" t="s">
         <v>5</v>
       </c>
-      <c r="I10" t="s">
-        <v>224</v>
+      <c r="I10">
+        <v>45</v>
       </c>
       <c r="J10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K10" t="s">
         <v>35</v>
@@ -1595,16 +1551,16 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="B11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C11" t="s">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="D11" t="s">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1618,14 +1574,14 @@
       <c r="H11" t="s">
         <v>36</v>
       </c>
-      <c r="I11" t="s">
-        <v>221</v>
+      <c r="I11">
+        <v>71</v>
       </c>
       <c r="J11" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L11" t="s">
         <v>3</v>
@@ -1642,16 +1598,16 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="B12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C12" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="D12" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1665,11 +1621,11 @@
       <c r="H12" t="s">
         <v>5</v>
       </c>
-      <c r="I12" t="s">
-        <v>108</v>
+      <c r="I12">
+        <v>89</v>
       </c>
       <c r="J12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K12" t="s">
         <v>67</v>
@@ -1689,16 +1645,16 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="B13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C13" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="D13" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1712,11 +1668,11 @@
       <c r="H13" t="s">
         <v>5</v>
       </c>
-      <c r="I13" t="s">
-        <v>149</v>
+      <c r="I13">
+        <v>56</v>
       </c>
       <c r="J13" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K13" t="s">
         <v>34</v>
@@ -1736,16 +1692,16 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="B14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C14" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="D14" t="s">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1759,14 +1715,14 @@
       <c r="H14" t="s">
         <v>5</v>
       </c>
-      <c r="I14" t="s">
-        <v>140</v>
+      <c r="I14">
+        <v>23</v>
       </c>
       <c r="J14" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="K14" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="L14" t="s">
         <v>34</v>
@@ -1783,16 +1739,16 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="B15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C15" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="D15" t="s">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1806,17 +1762,17 @@
       <c r="H15" t="s">
         <v>5</v>
       </c>
-      <c r="I15" t="s">
-        <v>153</v>
+      <c r="I15">
+        <v>73</v>
       </c>
       <c r="J15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K15" t="s">
         <v>15</v>
       </c>
       <c r="L15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M15" t="s">
         <v>14</v>
@@ -1830,16 +1786,16 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="B16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C16" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D16" t="s">
-        <v>211</v>
+        <v>195</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1853,14 +1809,14 @@
       <c r="H16" t="s">
         <v>5</v>
       </c>
-      <c r="I16" t="s">
-        <v>127</v>
+      <c r="I16">
+        <v>34</v>
       </c>
       <c r="J16" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L16" t="s">
         <v>62</v>
@@ -1877,16 +1833,16 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="B17" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C17" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="D17" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1900,11 +1856,11 @@
       <c r="H17" t="s">
         <v>5</v>
       </c>
-      <c r="I17" t="s">
-        <v>125</v>
+      <c r="I17">
+        <v>19</v>
       </c>
       <c r="J17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K17" t="s">
         <v>10</v>
@@ -1924,16 +1880,16 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="B18" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C18" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
       <c r="D18" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1947,8 +1903,8 @@
       <c r="H18" t="s">
         <v>36</v>
       </c>
-      <c r="I18" t="s">
-        <v>143</v>
+      <c r="I18">
+        <v>29</v>
       </c>
       <c r="J18" t="s">
         <v>50</v>
@@ -1971,16 +1927,16 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="B19" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C19" t="s">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="D19" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1994,14 +1950,14 @@
       <c r="H19" t="s">
         <v>5</v>
       </c>
-      <c r="I19" t="s">
-        <v>204</v>
+      <c r="I19">
+        <v>48</v>
       </c>
       <c r="J19" t="s">
         <v>11</v>
       </c>
       <c r="K19" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L19" t="s">
         <v>1</v>
@@ -2018,16 +1974,16 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="B20" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C20" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="D20" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -2041,8 +1997,8 @@
       <c r="H20" t="s">
         <v>5</v>
       </c>
-      <c r="I20" t="s">
-        <v>120</v>
+      <c r="I20">
+        <v>94</v>
       </c>
       <c r="J20" t="s">
         <v>52</v>
@@ -2051,7 +2007,7 @@
         <v>20</v>
       </c>
       <c r="L20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="M20" t="s">
         <v>9</v>
@@ -2065,16 +2021,16 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="B21" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C21" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="D21" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -2088,8 +2044,8 @@
       <c r="H21" t="s">
         <v>5</v>
       </c>
-      <c r="I21" t="s">
-        <v>70</v>
+      <c r="I21">
+        <v>91</v>
       </c>
       <c r="J21" t="s">
         <v>59</v>
@@ -2098,7 +2054,7 @@
         <v>47</v>
       </c>
       <c r="L21" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M21" t="s">
         <v>14</v>
@@ -2112,16 +2068,16 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="B22" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C22" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="D22" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -2135,17 +2091,17 @@
       <c r="H22" t="s">
         <v>5</v>
       </c>
-      <c r="I22" t="s">
-        <v>126</v>
+      <c r="I22">
+        <v>95</v>
       </c>
       <c r="J22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K22" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L22" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="M22" t="s">
         <v>1</v>
@@ -2159,16 +2115,16 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="B23" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C23" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="D23" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -2186,7 +2142,7 @@
         <v>57</v>
       </c>
       <c r="J23" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="K23" t="s">
         <v>3</v>
@@ -2206,16 +2162,16 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="B24" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C24" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="D24" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -2230,10 +2186,10 @@
         <v>5</v>
       </c>
       <c r="I24" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J24" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="K24" t="s">
         <v>41</v>
@@ -2253,16 +2209,16 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="B25" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C25" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="D25" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -2277,10 +2233,10 @@
         <v>5</v>
       </c>
       <c r="I25" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="J25" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K25" t="s">
         <v>34</v>
@@ -2300,16 +2256,16 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="B26" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C26" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="D26" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -2324,10 +2280,10 @@
         <v>36</v>
       </c>
       <c r="I26" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="J26" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K26" t="s">
         <v>40</v>
@@ -2347,34 +2303,34 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="B27" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C27" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="D27" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G27" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H27" t="s">
         <v>5</v>
       </c>
       <c r="I27" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="J27" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K27" t="s">
         <v>18</v>
@@ -2394,16 +2350,16 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="B28" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C28" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="D28" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -2418,16 +2374,16 @@
         <v>5</v>
       </c>
       <c r="I28" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="J28" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="K28" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="L28" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="M28" t="s">
         <v>21</v>
@@ -2441,16 +2397,16 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="B29" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C29" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="D29" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -2465,13 +2421,13 @@
         <v>5</v>
       </c>
       <c r="I29" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="J29" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="K29" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L29" t="s">
         <v>21</v>
@@ -2488,16 +2444,16 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="B30" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C30" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="D30" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -2512,16 +2468,16 @@
         <v>5</v>
       </c>
       <c r="I30" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="J30" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K30" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L30" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="M30" t="s">
         <v>2</v>
@@ -2535,16 +2491,16 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="B31" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C31" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="D31" t="s">
-        <v>179</v>
+        <v>238</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
@@ -2559,7 +2515,7 @@
         <v>5</v>
       </c>
       <c r="I31" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="J31" t="s">
         <v>65</v>
@@ -2582,16 +2538,16 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="B32" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C32" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="D32" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
@@ -2606,7 +2562,7 @@
         <v>36</v>
       </c>
       <c r="I32" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="J32" t="s">
         <v>53</v>
@@ -2629,16 +2585,16 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="B33" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C33" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="D33" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
@@ -2653,13 +2609,13 @@
         <v>5</v>
       </c>
       <c r="I33" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="J33" t="s">
         <v>27</v>
       </c>
       <c r="K33" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L33" t="s">
         <v>16</v>
@@ -2676,16 +2632,16 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="B34" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C34" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="D34" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -2723,16 +2679,16 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>142</v>
+      </c>
+      <c r="B35" t="s">
+        <v>101</v>
+      </c>
+      <c r="C35" t="s">
+        <v>157</v>
+      </c>
+      <c r="D35" t="s">
         <v>156</v>
-      </c>
-      <c r="B35" t="s">
-        <v>102</v>
-      </c>
-      <c r="C35" t="s">
-        <v>171</v>
-      </c>
-      <c r="D35" t="s">
-        <v>170</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -2747,7 +2703,7 @@
         <v>5</v>
       </c>
       <c r="I35" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="J35" t="s">
         <v>66</v>
@@ -2770,16 +2726,16 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="B36" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C36" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="D36" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
@@ -2794,16 +2750,16 @@
         <v>5</v>
       </c>
       <c r="I36" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J36" t="s">
         <v>51</v>
       </c>
       <c r="K36" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="L36" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M36" t="s">
         <v>34</v>
@@ -2817,16 +2773,16 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="B37" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C37" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="D37" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
@@ -2841,13 +2797,13 @@
         <v>5</v>
       </c>
       <c r="I37" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="J37" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="K37" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L37" t="s">
         <v>9</v>
@@ -2864,16 +2820,16 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="B38" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C38" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="D38" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
@@ -2888,13 +2844,13 @@
         <v>5</v>
       </c>
       <c r="I38" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="J38" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="K38" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="L38" t="s">
         <v>39</v>
@@ -2911,16 +2867,16 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="B39" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C39" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="D39" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
@@ -2938,10 +2894,10 @@
         <v>4</v>
       </c>
       <c r="J39" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K39" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L39" t="s">
         <v>2</v>
@@ -2958,16 +2914,16 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="B40" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C40" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="D40" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
@@ -2982,10 +2938,10 @@
         <v>5</v>
       </c>
       <c r="I40" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="J40" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K40" t="s">
         <v>10</v>
@@ -3005,16 +2961,16 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="B41" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C41" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="D41" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
@@ -3029,13 +2985,13 @@
         <v>5</v>
       </c>
       <c r="I41" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="J41" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K41" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L41" t="s">
         <v>56</v>
@@ -3052,16 +3008,16 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="B42" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C42" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="D42" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="E42" t="s">
         <v>8</v>
@@ -3076,16 +3032,16 @@
         <v>5</v>
       </c>
       <c r="I42" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="J42" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K42" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="L42" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="M42" t="s">
         <v>1</v>
@@ -3102,13 +3058,13 @@
         <v>19</v>
       </c>
       <c r="B43" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C43" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D43" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
@@ -3126,13 +3082,13 @@
         <v>69</v>
       </c>
       <c r="J43" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="K43" t="s">
         <v>64</v>
       </c>
       <c r="L43" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="M43" t="s">
         <v>13</v>
@@ -3149,13 +3105,13 @@
         <v>19</v>
       </c>
       <c r="B44" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C44" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D44" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
@@ -3170,13 +3126,13 @@
         <v>5</v>
       </c>
       <c r="I44" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="J44" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K44" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L44" t="s">
         <v>18</v>
@@ -3196,13 +3152,13 @@
         <v>19</v>
       </c>
       <c r="B45" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C45" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D45" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
@@ -3217,13 +3173,13 @@
         <v>5</v>
       </c>
       <c r="I45" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J45" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K45" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L45" t="s">
         <v>46</v>
